--- a/p6_deployment/data/france/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/p6_deployment/data/france/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2420"/>
+  <dimension ref="A1:C2428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36748,6 +36748,134 @@
         <v>259</v>
       </c>
     </row>
+    <row r="2421">
+      <c r="A2421" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2421" t="inlineStr">
+        <is>
+          <t xml:space="preserve">letexier f 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2421" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2422">
+      <c r="A2422" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2422" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brisard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2422" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2423">
+      <c r="A2423" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2423" t="inlineStr">
+        <is>
+          <t xml:space="preserve">letexier f 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2423" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2424">
+      <c r="A2424" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B2424" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
+        </is>
+      </c>
+      <c r="C2424" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2425">
+      <c r="A2425" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B2425" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
+        </is>
+      </c>
+      <c r="C2425" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2426">
+      <c r="A2426" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B2426" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
+        </is>
+      </c>
+      <c r="C2426" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2427">
+      <c r="A2427" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B2427" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
+        </is>
+      </c>
+      <c r="C2427" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2428">
+      <c r="A2428" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B2428" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="C2428" t="n">
+        <v>134</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
